--- a/data/bills/user1_bills.xlsx
+++ b/data/bills/user1_bills.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I103"/>
+  <dimension ref="A1:I104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,7 +477,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -485,38 +485,38 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>622</v>
+        <v>11133</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>06:00-12:00</t>
+          <t>00:00-06:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>微信</t>
+          <t>测试吃饭</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>学习</t>
+          <t>购物</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-04-25 14:47:54</t>
+          <t>2026-04-25 15:51:07</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-04-25 14:47:54</t>
+          <t>2026-04-25 15:51:07</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -524,38 +524,42 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.3</v>
+        <v>6000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>18:00-24:00</t>
+          <t>00:00-06:00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>测试吃饭</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>餐饮</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>测试不吃法</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>测试中</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-04-25 13:04:01</t>
+          <t>2026-04-25 15:45:18</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-04-25 13:04:01</t>
+          <t>2026-04-25 15:45:18</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -563,81 +567,77 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>218.17</v>
+        <v>622</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>12:00-18:00</t>
+          <t>06:00-12:00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>花呗</t>
+          <t>微信</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>购物</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>打车</t>
-        </is>
-      </c>
+          <t>学习</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-04-25 13:04:00</t>
+          <t>2026-04-25 14:47:54</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-04-25 13:04:00</t>
+          <t>2026-04-25 14:47:54</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2132.48</v>
+        <v>21.3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>06:00-12:00</t>
+          <t>18:00-24:00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>云闪付</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>转账</t>
+          <t>餐饮</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-04-25 13:04:00</t>
+          <t>2026-04-25 13:04:01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-04-25 13:04:00</t>
+          <t>2026-04-25 13:04:01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -645,24 +645,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>266.78</v>
+        <v>218.17</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00:00-06:00</t>
+          <t>12:00-18:00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>银行卡</t>
+          <t>花呗</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>娱乐</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>购物</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>打车</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>2026-04-25 13:04:00</t>
@@ -676,15 +680,15 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>61.87</v>
+        <v>2132.48</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -693,19 +697,15 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>银行卡</t>
+          <t>云闪付</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>日用品</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>超市购物</t>
-        </is>
-      </c>
+          <t>转账</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>2026-04-25 13:04:00</t>
@@ -719,7 +719,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -727,28 +727,24 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>209.33</v>
+        <v>500</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12:00-18:00</t>
+          <t>00:00-06:00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>微信</t>
+          <t>银行卡</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>学习</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>KTV</t>
-        </is>
-      </c>
+          <t>娱乐</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>2026-04-25 13:04:00</t>
@@ -756,13 +752,13 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-04-25 13:04:00</t>
+          <t>2026-04-25 15:51:31</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -770,26 +766,26 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>39.2</v>
+        <v>61.87</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>12:00-18:00</t>
+          <t>06:00-12:00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>支付宝</t>
+          <t>银行卡</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>日用品</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>药品</t>
+          <t>超市购物</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -805,7 +801,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -813,7 +809,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>59.69</v>
+        <v>209.33</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -822,12 +818,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>微信</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>日用品</t>
+          <t>学习</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -848,7 +844,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -856,38 +852,42 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>53.13</v>
+        <v>39.2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>00:00-06:00</t>
+          <t>12:00-18:00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>现金</t>
+          <t>支付宝</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>交通</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>药品</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:59</t>
+          <t>2026-04-25 13:04:00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:59</t>
+          <t>2026-04-25 13:04:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -895,42 +895,42 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>379.05</v>
+        <v>59.69</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>06:00-12:00</t>
+          <t>12:00-18:00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>云闪付</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>学习</t>
+          <t>日用品</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>药品</t>
+          <t>KTV</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:59</t>
+          <t>2026-04-25 13:04:00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:59</t>
+          <t>2026-04-25 13:04:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>104.28</v>
+        <v>53.13</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -947,19 +947,15 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>云闪付</t>
+          <t>现金</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>餐饮</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>超市购物</t>
-        </is>
-      </c>
+          <t>交通</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>2026-04-25 13:03:59</t>
@@ -973,7 +969,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -981,24 +977,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>68.53</v>
+        <v>379.05</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>18:00-24:00</t>
+          <t>06:00-12:00</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>云闪付</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>日用品</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>学习</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>药品</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>2026-04-25 13:03:59</t>
@@ -1012,15 +1012,15 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10067.39</v>
+        <v>104.28</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>奖金</t>
+          <t>餐饮</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>红包</t>
+          <t>超市购物</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1055,36 +1055,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2478.08</v>
+        <v>68.53</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>06:00-12:00</t>
+          <t>18:00-24:00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>现金</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>转账</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>朋友转账</t>
-        </is>
-      </c>
+          <t>日用品</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>2026-04-25 13:03:59</t>
@@ -1098,15 +1094,15 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>108.7</v>
+        <v>10067.39</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1115,17 +1111,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>云闪付</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>餐饮</t>
+          <t>奖金</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>学费</t>
+          <t>红包</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1141,19 +1137,19 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>171.7</v>
+        <v>2478.08</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>12:00-18:00</t>
+          <t>06:00-12:00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1163,28 +1159,28 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>水电</t>
+          <t>转账</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>药品</t>
+          <t>朋友转账</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:58</t>
+          <t>2026-04-25 13:03:59</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:58</t>
+          <t>2026-04-25 13:03:59</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1192,11 +1188,11 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>51.71</v>
+        <v>108.7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>06:00-12:00</t>
+          <t>00:00-06:00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1206,28 +1202,28 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>水电</t>
+          <t>餐饮</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>书籍</t>
+          <t>学费</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:58</t>
+          <t>2026-04-25 13:03:59</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:58</t>
+          <t>2026-04-25 13:03:59</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1235,26 +1231,26 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>350.09</v>
+        <v>171.7</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>06:00-12:00</t>
+          <t>12:00-18:00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>云闪付</t>
+          <t>现金</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>购物</t>
+          <t>水电</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>药品</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1270,7 +1266,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1278,26 +1274,26 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>124.38</v>
+        <v>51.71</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>12:00-18:00</t>
+          <t>06:00-12:00</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>云闪付</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>学习</t>
+          <t>水电</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>医院挂号</t>
+          <t>书籍</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1313,7 +1309,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1321,26 +1317,26 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>352.41</v>
+        <v>350.09</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>00:00-06:00</t>
+          <t>06:00-12:00</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>花呗</t>
+          <t>云闪付</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>购物</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>零食</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1356,7 +1352,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1364,26 +1360,26 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>245.9</v>
+        <v>124.38</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>18:00-24:00</t>
+          <t>12:00-18:00</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>银行卡</t>
+          <t>云闪付</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>娱乐</t>
+          <t>学习</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>晚餐</t>
+          <t>医院挂号</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1399,7 +1395,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1407,7 +1403,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>363.53</v>
+        <v>352.41</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1416,33 +1412,33 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>银行卡</t>
+          <t>花呗</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>购物</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>游戏充值</t>
+          <t>零食</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:57</t>
+          <t>2026-04-25 13:03:58</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:57</t>
+          <t>2026-04-25 13:03:58</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1450,7 +1446,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2008.42</v>
+        <v>245.9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1464,7 +1460,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>房租</t>
+          <t>娱乐</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1474,18 +1470,18 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:57</t>
+          <t>2026-04-25 13:03:58</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:57</t>
+          <t>2026-04-25 13:03:58</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1493,26 +1489,26 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>143.86</v>
+        <v>363.53</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>12:00-18:00</t>
+          <t>00:00-06:00</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>现金</t>
+          <t>银行卡</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>日用品</t>
+          <t>购物</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>零食</t>
+          <t>游戏充值</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1528,34 +1524,34 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5365.15</v>
+        <v>2008.42</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>06:00-12:00</t>
+          <t>18:00-24:00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>信用卡</t>
+          <t>银行卡</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>工资</t>
+          <t>房租</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>项目奖金</t>
+          <t>晚餐</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1571,7 +1567,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1579,26 +1575,26 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27.91</v>
+        <v>143.86</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>00:00-06:00</t>
+          <t>12:00-18:00</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>微信</t>
+          <t>现金</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>餐饮</t>
+          <t>日用品</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>网费</t>
+          <t>零食</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1614,15 +1610,15 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>72.64</v>
+        <v>5365.15</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1631,17 +1627,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>花呗</t>
+          <t>信用卡</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>交通</t>
+          <t>工资</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>书籍</t>
+          <t>项目奖金</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1657,7 +1653,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1665,24 +1661,28 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>57.91</v>
+        <v>27.91</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>06:00-12:00</t>
+          <t>00:00-06:00</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>微信</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>日用品</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>餐饮</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>网费</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>2026-04-25 13:03:57</t>
@@ -1696,7 +1696,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1704,81 +1704,81 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>153.57</v>
+        <v>72.64</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>00:00-06:00</t>
+          <t>06:00-12:00</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>微信</t>
+          <t>花呗</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>餐饮</t>
+          <t>交通</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>水果</t>
+          <t>书籍</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:56</t>
+          <t>2026-04-25 13:03:57</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:56</t>
+          <t>2026-04-25 13:03:57</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>11075.92</v>
+        <v>57.91</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>00:00-06:00</t>
+          <t>06:00-12:00</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>花呗</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>奖金</t>
+          <t>日用品</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:56</t>
+          <t>2026-04-25 13:03:57</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:56</t>
+          <t>2026-04-25 13:03:57</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1786,26 +1786,26 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>341.37</v>
+        <v>153.57</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>12:00-18:00</t>
+          <t>00:00-06:00</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>云闪付</t>
+          <t>微信</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>餐饮</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>水费</t>
+          <t>水果</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1821,15 +1821,15 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>279.91</v>
+        <v>11075.92</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1843,12 +1843,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>娱乐</t>
+          <t>奖金</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>水果</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1858,38 +1858,42 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:56</t>
+          <t>2026-04-25 15:50:31</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>14138.94</v>
+        <v>341.37</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>06:00-12:00</t>
+          <t>12:00-18:00</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>现金</t>
+          <t>云闪付</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>转账</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>水费</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>2026-04-25 13:03:56</t>
@@ -1903,7 +1907,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1911,24 +1915,28 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>75.37</v>
+        <v>279.91</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>18:00-24:00</t>
+          <t>00:00-06:00</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>支付宝</t>
+          <t>花呗</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>交通</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+          <t>娱乐</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>水果</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>2026-04-25 13:03:56</t>
@@ -1942,36 +1950,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>76</v>
+        <v>14138.94</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>00:00-06:00</t>
+          <t>06:00-12:00</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>银行卡</t>
+          <t>现金</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>交通</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>外卖</t>
-        </is>
-      </c>
+          <t>转账</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>2026-04-25 13:03:56</t>
@@ -1985,29 +1989,29 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1450.51</v>
+        <v>75.37</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>00:00-06:00</t>
+          <t>18:00-24:00</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>花呗</t>
+          <t>支付宝</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>工资</t>
+          <t>交通</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -2024,7 +2028,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -2032,11 +2036,11 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>65.34</v>
+        <v>76</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>12:00-18:00</t>
+          <t>00:00-06:00</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2046,32 +2050,36 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>日用品</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+          <t>交通</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>外卖</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:55</t>
+          <t>2026-04-25 13:03:56</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:55</t>
+          <t>2026-04-25 13:03:56</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>37.13</v>
+        <v>1450.51</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2080,29 +2088,29 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>现金</t>
+          <t>花呗</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>日用品</t>
+          <t>工资</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:55</t>
+          <t>2026-04-25 13:03:56</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:55</t>
+          <t>2026-04-25 13:03:56</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2110,28 +2118,24 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>281.73</v>
+        <v>65.34</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>18:00-24:00</t>
+          <t>12:00-18:00</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>银行卡</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>娱乐</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>网购</t>
-        </is>
-      </c>
+          <t>日用品</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>2026-04-25 13:03:55</t>
@@ -2145,7 +2149,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2153,7 +2157,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>446.13</v>
+        <v>37.13</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2162,12 +2166,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>银行卡</t>
+          <t>现金</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>日用品</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -2184,32 +2188,36 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>14015.47</v>
+        <v>281.73</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>00:00-06:00</t>
+          <t>18:00-24:00</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>微信</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>娱乐</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>网购</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>2026-04-25 13:03:55</t>
@@ -2223,19 +2231,19 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>11909.86</v>
+        <v>446.13</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>12:00-18:00</t>
+          <t>00:00-06:00</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2245,14 +2253,10 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>理财收益</t>
-        </is>
-      </c>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>2026-04-25 13:03:55</t>
@@ -2266,29 +2270,29 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3131.02</v>
+        <v>14015.47</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>06:00-12:00</t>
+          <t>00:00-06:00</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>微信</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>其他</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>房租</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -2305,34 +2309,34 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>202.08</v>
+        <v>11909.86</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>18:00-24:00</t>
+          <t>12:00-18:00</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>云闪付</t>
+          <t>银行卡</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>学习</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>医院挂号</t>
+          <t>理财收益</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2348,7 +2352,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2356,7 +2360,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>20.08</v>
+        <v>3131.02</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2365,72 +2369,72 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>银行卡</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>交通</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>零食</t>
-        </is>
-      </c>
+          <t>房租</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:54</t>
+          <t>2026-04-25 13:03:55</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:54</t>
+          <t>2026-04-25 13:03:55</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>9063.799999999999</v>
+        <v>202.08</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>06:00-12:00</t>
+          <t>18:00-24:00</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>信用卡</t>
+          <t>云闪付</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>奖金</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+          <t>学习</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>医院挂号</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:54</t>
+          <t>2026-04-25 13:03:55</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:54</t>
+          <t>2026-04-25 13:03:55</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2438,24 +2442,28 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>98.20999999999999</v>
+        <v>20.08</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>00:00-06:00</t>
+          <t>06:00-12:00</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>银行卡</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>学习</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
+          <t>交通</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>零食</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>2026-04-25 13:03:54</t>
@@ -2469,36 +2477,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>101.68</v>
+        <v>9063.799999999999</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>18:00-24:00</t>
+          <t>06:00-12:00</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>花呗</t>
+          <t>信用卡</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>学习</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>书籍</t>
-        </is>
-      </c>
+          <t>奖金</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>2026-04-25 13:03:54</t>
@@ -2512,7 +2516,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2520,7 +2524,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>133.34</v>
+        <v>98.20999999999999</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2534,7 +2538,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>购物</t>
+          <t>学习</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -2551,34 +2555,34 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>9385.139999999999</v>
+        <v>101.68</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>00:00-06:00</t>
+          <t>18:00-24:00</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>支付宝</t>
+          <t>花呗</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>工资</t>
+          <t>学习</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>朋友转账</t>
+          <t>书籍</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2594,7 +2598,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2602,7 +2606,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>321.42</v>
+        <v>133.34</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2611,7 +2615,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>银行卡</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2619,11 +2623,7 @@
           <t>购物</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>晚餐</t>
-        </is>
-      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>2026-04-25 13:03:54</t>
@@ -2637,7 +2637,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2645,24 +2645,28 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>7863.84</v>
+        <v>9385.139999999999</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>18:00-24:00</t>
+          <t>00:00-06:00</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>支付宝</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>奖金</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+          <t>工资</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>朋友转账</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>2026-04-25 13:03:54</t>
@@ -2676,7 +2680,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -2684,7 +2688,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>76.86</v>
+        <v>321.42</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2693,17 +2697,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>支付宝</t>
+          <t>银行卡</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>日用品</t>
+          <t>购物</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>共享单车</t>
+          <t>晚餐</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2719,50 +2723,46 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>91.33</v>
+        <v>7863.84</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>12:00-18:00</t>
+          <t>18:00-24:00</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>信用卡</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>日用品</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>药品</t>
-        </is>
-      </c>
+          <t>奖金</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:53</t>
+          <t>2026-04-25 13:03:54</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:53</t>
+          <t>2026-04-25 13:03:54</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2770,16 +2770,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>124.49</v>
+        <v>76.86</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>12:00-18:00</t>
+          <t>00:00-06:00</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>微信</t>
+          <t>支付宝</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2787,21 +2787,25 @@
           <t>日用品</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>共享单车</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:53</t>
+          <t>2026-04-25 13:03:54</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:53</t>
+          <t>2026-04-25 13:03:54</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2809,26 +2813,26 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3631.78</v>
+        <v>91.33</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>18:00-24:00</t>
+          <t>12:00-18:00</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>微信</t>
+          <t>信用卡</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>房租</t>
+          <t>日用品</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>打车</t>
+          <t>药品</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2844,7 +2848,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2852,28 +2856,24 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1523.1</v>
+        <v>124.49</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>06:00-12:00</t>
+          <t>12:00-18:00</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>微信</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>房租</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>午餐</t>
-        </is>
-      </c>
+          <t>日用品</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>2026-04-25 13:03:53</t>
@@ -2887,7 +2887,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>31.33</v>
+        <v>3631.78</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2904,17 +2904,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>云闪付</t>
+          <t>微信</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>房租</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>网费</t>
+          <t>打车</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2930,7 +2930,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2938,26 +2938,26 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>14.96</v>
+        <v>1523.1</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>18:00-24:00</t>
+          <t>06:00-12:00</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>现金</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>交通</t>
+          <t>房租</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>KTV</t>
+          <t>午餐</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2973,7 +2973,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2981,21 +2981,21 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>70.53</v>
+        <v>31.33</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>12:00-18:00</t>
+          <t>18:00-24:00</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>云闪付</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>餐饮</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3016,7 +3016,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>295.46</v>
+        <v>14.96</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -3033,17 +3033,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>花呗</t>
+          <t>现金</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>娱乐</t>
+          <t>交通</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>超市购物</t>
+          <t>KTV</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3059,7 +3059,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -3067,24 +3067,28 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>106.02</v>
+        <v>70.53</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>06:00-12:00</t>
+          <t>12:00-18:00</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>信用卡</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>日用品</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
+          <t>餐饮</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>网费</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>2026-04-25 13:03:53</t>
@@ -3098,7 +3102,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -3106,26 +3110,26 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>126.73</v>
+        <v>295.46</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>12:00-18:00</t>
+          <t>18:00-24:00</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>支付宝</t>
+          <t>花呗</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>水电</t>
+          <t>娱乐</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>早餐</t>
+          <t>超市购物</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3141,7 +3145,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -3149,38 +3153,38 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>142.3</v>
+        <v>106.02</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>12:00-18:00</t>
+          <t>06:00-12:00</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>花呗</t>
+          <t>信用卡</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>餐饮</t>
+          <t>日用品</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:52</t>
+          <t>2026-04-25 13:03:53</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:52</t>
+          <t>2026-04-25 13:03:53</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -3188,71 +3192,67 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>55</v>
+        <v>126.73</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>06:00-12:00</t>
+          <t>12:00-18:00</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>现金</t>
+          <t>支付宝</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>交通</t>
+          <t>水电</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>早餐</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:52</t>
+          <t>2026-04-25 13:03:53</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:52</t>
+          <t>2026-04-25 13:03:53</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>4249.02</v>
+        <v>142.3</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>18:00-24:00</t>
+          <t>12:00-18:00</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>花呗</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>转账</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>项目奖金</t>
-        </is>
-      </c>
+          <t>餐饮</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>2026-04-25 13:03:52</t>
@@ -3266,15 +3266,15 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>12668.54</v>
+        <v>55</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>奖金</t>
+          <t>交通</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>月度工资</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3309,15 +3309,15 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>113.16</v>
+        <v>4249.02</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -3326,15 +3326,19 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>银行卡</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>娱乐</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr"/>
+          <t>转账</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>项目奖金</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>2026-04-25 13:03:52</t>
@@ -3348,34 +3352,34 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>99.03</v>
+        <v>12668.54</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>00:00-06:00</t>
+          <t>06:00-12:00</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>银行卡</t>
+          <t>现金</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>日用品</t>
+          <t>奖金</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>其他支出</t>
+          <t>月度工资</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3391,29 +3395,29 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>13424.99</v>
+        <v>113.16</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>12:00-18:00</t>
+          <t>18:00-24:00</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>现金</t>
+          <t>银行卡</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>工资</t>
+          <t>娱乐</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -3430,7 +3434,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -3438,7 +3442,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>228.9</v>
+        <v>99.03</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -3447,15 +3451,19 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>银行卡</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>购物</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr"/>
+          <t>日用品</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>其他支出</t>
+        </is>
+      </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>2026-04-25 13:03:52</t>
@@ -3469,36 +3477,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>41.28</v>
+        <v>13424.99</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>06:00-12:00</t>
+          <t>12:00-18:00</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>支付宝</t>
+          <t>现金</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>晚餐</t>
-        </is>
-      </c>
+          <t>工资</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
           <t>2026-04-25 13:03:52</t>
@@ -3512,7 +3516,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -3520,21 +3524,21 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>135.16</v>
+        <v>228.9</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>18:00-24:00</t>
+          <t>00:00-06:00</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>微信</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>学习</t>
+          <t>购物</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -3551,7 +3555,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -3559,11 +3563,11 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>476.07</v>
+        <v>41.28</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>00:00-06:00</t>
+          <t>06:00-12:00</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3573,24 +3577,28 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>购物</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr"/>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>晚餐</t>
+        </is>
+      </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:51</t>
+          <t>2026-04-25 13:03:52</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:51</t>
+          <t>2026-04-25 13:03:52</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -3598,7 +3606,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>65.92</v>
+        <v>135.16</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -3607,33 +3615,29 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>云闪付</t>
+          <t>微信</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>共享单车</t>
-        </is>
-      </c>
+          <t>学习</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:51</t>
+          <t>2026-04-25 13:03:52</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:51</t>
+          <t>2026-04-25 13:03:52</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -3641,11 +3645,11 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3821.37</v>
+        <v>476.07</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>06:00-12:00</t>
+          <t>00:00-06:00</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3655,14 +3659,10 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>房租</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>地铁</t>
-        </is>
-      </c>
+          <t>购物</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
           <t>2026-04-25 13:03:51</t>
@@ -3676,7 +3676,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -3684,26 +3684,26 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>82.64</v>
+        <v>65.92</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>06:00-12:00</t>
+          <t>18:00-24:00</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>花呗</t>
+          <t>云闪付</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>日用品</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>零食</t>
+          <t>共享单车</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3719,7 +3719,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -3727,24 +3727,28 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>122.53</v>
+        <v>3821.37</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>12:00-18:00</t>
+          <t>06:00-12:00</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>微信</t>
+          <t>支付宝</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>学习</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr"/>
+          <t>房租</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>地铁</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>2026-04-25 13:03:51</t>
@@ -3758,7 +3762,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -3766,24 +3770,28 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>159.72</v>
+        <v>82.64</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>18:00-24:00</t>
+          <t>06:00-12:00</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>花呗</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>餐饮</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr"/>
+          <t>日用品</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>零食</t>
+        </is>
+      </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>2026-04-25 13:03:51</t>
@@ -3797,7 +3805,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -3805,28 +3813,24 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>3752.17</v>
+        <v>122.53</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>06:00-12:00</t>
+          <t>12:00-18:00</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>花呗</t>
+          <t>微信</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>房租</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>医院挂号</t>
-        </is>
-      </c>
+          <t>学习</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>2026-04-25 13:03:51</t>
@@ -3840,7 +3844,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -3848,28 +3852,24 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>63.85</v>
+        <v>159.72</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>06:00-12:00</t>
+          <t>18:00-24:00</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>银行卡</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>医疗</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>外卖</t>
-        </is>
-      </c>
+          <t>餐饮</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
           <t>2026-04-25 13:03:51</t>
@@ -3883,7 +3883,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -3891,26 +3891,26 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>128.37</v>
+        <v>3752.17</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>00:00-06:00</t>
+          <t>06:00-12:00</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>现金</t>
+          <t>花呗</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>娱乐</t>
+          <t>房租</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>午餐</t>
+          <t>医院挂号</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3926,34 +3926,34 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>12454.05</v>
+        <v>63.85</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>18:00-24:00</t>
+          <t>06:00-12:00</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>银行卡</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>工资</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>兼职收入</t>
+          <t>外卖</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3969,7 +3969,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -3977,26 +3977,26 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>382.3</v>
+        <v>128.37</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>18:00-24:00</t>
+          <t>00:00-06:00</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>云闪付</t>
+          <t>现金</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>学习</t>
+          <t>娱乐</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>地铁</t>
+          <t>午餐</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4012,19 +4012,19 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>131.3</v>
+        <v>12454.05</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>12:00-18:00</t>
+          <t>18:00-24:00</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>工资</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>零食</t>
+          <t>兼职收入</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4055,46 +4055,50 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>9787.32</v>
+        <v>382.3</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>00:00-06:00</t>
+          <t>18:00-24:00</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>现金</t>
+          <t>云闪付</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>奖金</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr"/>
+          <t>学习</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>地铁</t>
+        </is>
+      </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:50</t>
+          <t>2026-04-25 13:03:51</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:50</t>
+          <t>2026-04-25 13:03:51</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -4102,71 +4106,67 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>387.13</v>
+        <v>131.3</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>18:00-24:00</t>
+          <t>12:00-18:00</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>信用卡</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>学习</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>午餐</t>
+          <t>零食</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:50</t>
+          <t>2026-04-25 13:03:51</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2026-04-25 13:03:50</t>
+          <t>2026-04-25 13:03:51</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>271.04</v>
+        <v>9787.32</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>06:00-12:00</t>
+          <t>00:00-06:00</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>现金</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>医疗</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>药品</t>
-        </is>
-      </c>
+          <t>奖金</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
           <t>2026-04-25 13:03:50</t>
@@ -4180,7 +4180,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>77.34</v>
+        <v>387.13</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -4197,17 +4197,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>花呗</t>
+          <t>信用卡</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>日用品</t>
+          <t>学习</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>零食</t>
+          <t>午餐</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4223,7 +4223,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -4231,26 +4231,26 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1711.1</v>
+        <v>271.04</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>00:00-06:00</t>
+          <t>06:00-12:00</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>花呗</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>房租</t>
+          <t>医疗</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>忘记记什么了</t>
+          <t>药品</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4266,34 +4266,34 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>11850.35</v>
+        <v>77.34</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>12:00-18:00</t>
+          <t>18:00-24:00</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>银行卡</t>
+          <t>花呗</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>日用品</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>兼职收入</t>
+          <t>零食</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4309,15 +4309,15 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>6846.35</v>
+        <v>1711.1</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -4331,10 +4331,14 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>兼职</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr"/>
+          <t>房租</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>忘记记什么了</t>
+        </is>
+      </c>
       <c r="H94" t="inlineStr">
         <is>
           <t>2026-04-25 13:03:50</t>
@@ -4348,15 +4352,15 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1342.06</v>
+        <v>11850.35</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -4365,17 +4369,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>花呗</t>
+          <t>银行卡</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>房租</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>外卖</t>
+          <t>兼职收入</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4391,7 +4395,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -4399,21 +4403,21 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>13440.45</v>
+        <v>6846.35</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>18:00-24:00</t>
+          <t>00:00-06:00</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>银行卡</t>
+          <t>花呗</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>转账</t>
+          <t>兼职</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
@@ -4430,7 +4434,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -4438,16 +4442,16 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3593.99</v>
+        <v>1342.06</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>18:00-24:00</t>
+          <t>12:00-18:00</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>云闪付</t>
+          <t>花呗</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4455,7 +4459,11 @@
           <t>房租</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>外卖</t>
+        </is>
+      </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>2026-04-25 13:03:50</t>
@@ -4469,36 +4477,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>63.51</v>
+        <v>13440.45</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>06:00-12:00</t>
+          <t>18:00-24:00</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>银行卡</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>购物</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>公交</t>
-        </is>
-      </c>
+          <t>转账</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
           <t>2026-04-25 13:03:50</t>
@@ -4512,29 +4516,29 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>12156.65</v>
+        <v>3593.99</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>06:00-12:00</t>
+          <t>18:00-24:00</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>支付宝</t>
+          <t>云闪付</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>工资</t>
+          <t>房租</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -4551,7 +4555,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -4559,26 +4563,26 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>57.69</v>
+        <v>63.51</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>00:00-06:00</t>
+          <t>06:00-12:00</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>云闪付</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>交通</t>
+          <t>购物</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>医院挂号</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4594,29 +4598,29 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>237.67</v>
+        <v>12156.65</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>18:00-24:00</t>
+          <t>06:00-12:00</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>花呗</t>
+          <t>支付宝</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>购物</t>
+          <t>工资</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
@@ -4633,7 +4637,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -4641,26 +4645,26 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>42.27</v>
+        <v>57.69</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>18:00-24:00</t>
+          <t>00:00-06:00</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>花呗</t>
+          <t>云闪付</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>医疗</t>
+          <t>交通</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>其他支出</t>
+          <t>医院挂号</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4676,7 +4680,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -4684,11 +4688,11 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>699.99</v>
+        <v>237.67</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>00:00-06:00</t>
+          <t>18:00-24:00</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4698,18 +4702,61 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>兼职</t>
+          <t>购物</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-04-25 14:58:49</t>
+          <t>2026-04-25 13:03:50</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2026-04-25 14:58:49</t>
+          <t>2026-04-25 13:03:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>15</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>支出</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>42.27</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>18:00-24:00</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>花呗</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>其他支出</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2026-04-25 13:03:50</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2026-04-25 13:03:50</t>
         </is>
       </c>
     </row>
